--- a/resources/qa_test/formula_merge_samples/match_stat.xlsx
+++ b/resources/qa_test/formula_merge_samples/match_stat.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,13 +643,6 @@
       <c r="H7">
         <f>MAX(B7:E7)</f>
         <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>帮我一次性配三样东西。</t>
-        </is>
       </c>
     </row>
   </sheetData>
